--- a/mistral_translate_work/split_by_prompt/excel/quest/lang_multi_text/lang_multi_text__quest__part_0017.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/quest/lang_multi_text/lang_multi_text__quest__part_0017.xlsx
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Endstate Matrix</t>
+          <t>Ma Trận Endstate</t>
         </is>
       </c>
     </row>
